--- a/salida/507843056_CORPORATIVO_EN_FARMACIAS_Y_SERVICIOS_ZH_SA_DE_CV/op_borrador.xlsx
+++ b/salida/507843056_CORPORATIVO_EN_FARMACIAS_Y_SERVICIOS_ZH_SA_DE_CV/op_borrador.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="70">
   <si>
     <t>Plan tarifario</t>
   </si>
@@ -221,6 +221,9 @@
     <t>AVENIDA SERDAN 80, INT LOCAL 3, GUAYMAS CENTRO, GUAYMAS, SONORA, 85400</t>
   </si>
   <si>
+    <t>240729MKT0305</t>
+  </si>
+  <si>
     <t xml:space="preserve"> PLAN 1299: REDES: Facebook; Intagram; Gmail; Google_maps; Outlook; X; Uber; WhatsApp (Texto);    STREAMING: Spotify; WhatsApp (Video); TikTok; 2 GB</t>
   </si>
   <si>
@@ -234,6 +237,9 @@
   </si>
   <si>
     <t>APPLE IPHONE 18 PRO MAX 256GB 5G, PLATA</t>
+  </si>
+  <si>
+    <t>CPP</t>
   </si>
   <si>
     <t>APPLE IPHONE 18 PRO MAX 256GB 5G, NEGRO ATT</t>
@@ -582,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -692,15 +698,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -711,15 +708,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -758,16 +746,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -788,6 +772,69 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2028,25 +2075,25 @@
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
       <c r="I8" s="25"/>
-      <c r="J8" s="60" t="s">
+      <c r="J8" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="56"/>
       <c r="M8" s="25"/>
-      <c r="N8" s="60" t="s">
+      <c r="N8" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="62"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="55"/>
+      <c r="Q8" s="56"/>
       <c r="R8" s="25"/>
-      <c r="S8" s="60" t="s">
+      <c r="S8" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="T8" s="61"/>
-      <c r="U8" s="61"/>
-      <c r="V8" s="62"/>
+      <c r="T8" s="55"/>
+      <c r="U8" s="55"/>
+      <c r="V8" s="56"/>
       <c r="W8" s="25"/>
       <c r="X8" s="38" t="s">
         <v>17</v>
@@ -2056,37 +2103,37 @@
     </row>
     <row r="9" spans="2:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B9" s="7"/>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76"/>
       <c r="I9" s="10"/>
-      <c r="J9" s="78">
+      <c r="J9" s="70">
         <v>507843056</v>
       </c>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="72"/>
       <c r="M9" s="10"/>
-      <c r="N9" s="75" t="s">
+      <c r="N9" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="77"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68"/>
+      <c r="Q9" s="69"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="64"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="65"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="58"/>
+      <c r="V9" s="59"/>
       <c r="W9" s="10"/>
-      <c r="X9" s="81" t="s">
+      <c r="X9" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="Y9" s="81"/>
+      <c r="Y9" s="73"/>
       <c r="Z9" s="9"/>
     </row>
     <row r="10" spans="2:26" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -2129,11 +2176,11 @@
       </c>
       <c r="H11" s="38"/>
       <c r="I11" s="25"/>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="56"/>
       <c r="M11" s="25"/>
       <c r="N11" s="38" t="s">
         <v>22</v>
@@ -2155,35 +2202,37 @@
     </row>
     <row r="12" spans="2:26" ht="24.65" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B12" s="7"/>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
+      <c r="G12" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="66"/>
       <c r="I12" s="8"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="65"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="59"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="74" t="s">
+      <c r="N12" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="74"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="79"/>
       <c r="R12" s="8"/>
-      <c r="S12" s="55" t="s">
+      <c r="S12" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="57"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="82"/>
       <c r="Z12" s="9"/>
     </row>
     <row r="13" spans="2:26" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -2228,10 +2277,10 @@
       <c r="M14" s="20"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
@@ -2308,32 +2357,32 @@
       <c r="C16" s="27">
         <v>1</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="58">
+      <c r="E16" s="90" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="52">
         <v>24</v>
       </c>
-      <c r="G16" s="59"/>
-      <c r="H16" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="71"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="92"/>
       <c r="J16" s="27">
         <v>31999</v>
       </c>
       <c r="K16" s="26">
-        <v>15240.82</v>
-      </c>
-      <c r="L16" s="58">
+        <v>27199</v>
+      </c>
+      <c r="L16" s="52">
         <v>24</v>
       </c>
-      <c r="M16" s="59"/>
+      <c r="M16" s="53"/>
       <c r="N16" s="26">
-        <v>698.26</v>
+        <v>200.01</v>
       </c>
       <c r="O16" s="26" t="s">
         <v>52</v>
@@ -2351,7 +2400,9 @@
       <c r="T16" s="26">
         <v>6221201372</v>
       </c>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28" t="s">
+        <v>66</v>
+      </c>
       <c r="V16" s="45" t="s">
         <v>52</v>
       </c>
@@ -2369,32 +2420,32 @@
       <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="90" t="s">
         <v>63</v>
+      </c>
+      <c r="E17" s="90" t="s">
+        <v>64</v>
       </c>
       <c r="F17" s="42">
         <v>24</v>
       </c>
       <c r="G17" s="43"/>
-      <c r="H17" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="34"/>
+      <c r="H17" s="93" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="94"/>
       <c r="J17" s="2">
         <v>31999</v>
       </c>
       <c r="K17" s="2">
-        <v>15240.82</v>
+        <v>27199</v>
       </c>
       <c r="L17" s="34">
         <v>24</v>
       </c>
       <c r="M17" s="34"/>
       <c r="N17" s="2">
-        <v>698.26</v>
+        <v>200.01</v>
       </c>
       <c r="O17" s="19" t="s">
         <v>52</v>
@@ -2412,7 +2463,9 @@
       <c r="T17" s="19">
         <v>6221090987</v>
       </c>
-      <c r="U17" s="2"/>
+      <c r="U17" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V17" s="34" t="s">
         <v>52</v>
       </c>
@@ -2430,32 +2483,32 @@
       <c r="C18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>66</v>
+      <c r="D18" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F18" s="42">
         <v>24</v>
       </c>
       <c r="G18" s="43"/>
-      <c r="H18" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="34"/>
+      <c r="H18" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="94"/>
       <c r="J18" s="2">
         <v>4999</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>52</v>
+      <c r="K18" s="2">
+        <v>1649</v>
       </c>
       <c r="L18" s="34">
         <v>24</v>
       </c>
       <c r="M18" s="34"/>
       <c r="N18" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O18" s="19" t="s">
         <v>52</v>
@@ -2473,7 +2526,9 @@
       <c r="T18" s="19">
         <v>6221155647</v>
       </c>
-      <c r="U18" s="2"/>
+      <c r="U18" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V18" s="34" t="s">
         <v>52</v>
       </c>
@@ -2491,32 +2546,32 @@
       <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>66</v>
+      <c r="D19" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F19" s="42">
         <v>24</v>
       </c>
       <c r="G19" s="43"/>
-      <c r="H19" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="34"/>
+      <c r="H19" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="94"/>
       <c r="J19" s="2">
         <v>4999</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>52</v>
+      <c r="K19" s="2">
+        <v>1649</v>
       </c>
       <c r="L19" s="34">
         <v>24</v>
       </c>
       <c r="M19" s="34"/>
       <c r="N19" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O19" s="19" t="s">
         <v>52</v>
@@ -2534,7 +2589,9 @@
       <c r="T19" s="19">
         <v>6221155645</v>
       </c>
-      <c r="U19" s="2"/>
+      <c r="U19" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V19" s="34" t="s">
         <v>52</v>
       </c>
@@ -2552,32 +2609,32 @@
       <c r="C20" s="2">
         <v>1</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>66</v>
+      <c r="D20" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F20" s="42">
         <v>24</v>
       </c>
       <c r="G20" s="43"/>
-      <c r="H20" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" s="34"/>
+      <c r="H20" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="94"/>
       <c r="J20" s="2">
         <v>4999</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>52</v>
+      <c r="K20" s="2">
+        <v>1649</v>
       </c>
       <c r="L20" s="34">
         <v>24</v>
       </c>
       <c r="M20" s="34"/>
       <c r="N20" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O20" s="19" t="s">
         <v>52</v>
@@ -2595,7 +2652,9 @@
       <c r="T20" s="19">
         <v>6221155658</v>
       </c>
-      <c r="U20" s="2"/>
+      <c r="U20" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V20" s="34" t="s">
         <v>52</v>
       </c>
@@ -2613,32 +2672,32 @@
       <c r="C21" s="2">
         <v>1</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>66</v>
+      <c r="D21" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F21" s="42">
         <v>24</v>
       </c>
       <c r="G21" s="43"/>
-      <c r="H21" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="34"/>
+      <c r="H21" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="94"/>
       <c r="J21" s="2">
         <v>4999</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>52</v>
+      <c r="K21" s="2">
+        <v>1649</v>
       </c>
       <c r="L21" s="34">
         <v>24</v>
       </c>
       <c r="M21" s="34"/>
       <c r="N21" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O21" s="19" t="s">
         <v>52</v>
@@ -2656,7 +2715,9 @@
       <c r="T21" s="19">
         <v>6221854808</v>
       </c>
-      <c r="U21" s="2"/>
+      <c r="U21" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V21" s="34" t="s">
         <v>52</v>
       </c>
@@ -2674,32 +2735,32 @@
       <c r="C22" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>66</v>
+      <c r="D22" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F22" s="42">
         <v>24</v>
       </c>
       <c r="G22" s="43"/>
-      <c r="H22" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="34"/>
+      <c r="H22" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="94"/>
       <c r="J22" s="2">
         <v>4999</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>52</v>
+      <c r="K22" s="2">
+        <v>1649</v>
       </c>
       <c r="L22" s="34">
         <v>24</v>
       </c>
       <c r="M22" s="34"/>
       <c r="N22" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O22" s="19" t="s">
         <v>52</v>
@@ -2717,7 +2778,9 @@
       <c r="T22" s="19">
         <v>6221155654</v>
       </c>
-      <c r="U22" s="2"/>
+      <c r="U22" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V22" s="34" t="s">
         <v>52</v>
       </c>
@@ -2735,32 +2798,32 @@
       <c r="C23" s="2">
         <v>1</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>66</v>
+      <c r="D23" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F23" s="42">
         <v>24</v>
       </c>
       <c r="G23" s="43"/>
-      <c r="H23" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="43"/>
+      <c r="H23" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="94"/>
       <c r="J23" s="2">
         <v>4999</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>52</v>
+      <c r="K23" s="2">
+        <v>1649</v>
       </c>
       <c r="L23" s="34">
         <v>24</v>
       </c>
       <c r="M23" s="34"/>
       <c r="N23" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>52</v>
@@ -2778,7 +2841,9 @@
       <c r="T23" s="2">
         <v>6221854809</v>
       </c>
-      <c r="U23" s="2"/>
+      <c r="U23" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V23" s="34" t="s">
         <v>52</v>
       </c>
@@ -2796,32 +2861,32 @@
       <c r="C24" s="2">
         <v>1</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>66</v>
+      <c r="D24" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F24" s="42">
         <v>24</v>
       </c>
       <c r="G24" s="43"/>
-      <c r="H24" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" s="34"/>
+      <c r="H24" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="94"/>
       <c r="J24" s="2">
         <v>4999</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>52</v>
+      <c r="K24" s="2">
+        <v>1649</v>
       </c>
       <c r="L24" s="34">
         <v>24</v>
       </c>
       <c r="M24" s="34"/>
       <c r="N24" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O24" s="19" t="s">
         <v>52</v>
@@ -2839,7 +2904,9 @@
       <c r="T24" s="19">
         <v>6221155655</v>
       </c>
-      <c r="U24" s="2"/>
+      <c r="U24" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V24" s="34" t="s">
         <v>52</v>
       </c>
@@ -2857,32 +2924,32 @@
       <c r="C25" s="2">
         <v>1</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>66</v>
+      <c r="D25" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F25" s="42">
         <v>24</v>
       </c>
       <c r="G25" s="43"/>
-      <c r="H25" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I25" s="34"/>
+      <c r="H25" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="94"/>
       <c r="J25" s="2">
         <v>4999</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>52</v>
+      <c r="K25" s="2">
+        <v>1649</v>
       </c>
       <c r="L25" s="34">
         <v>24</v>
       </c>
       <c r="M25" s="34"/>
       <c r="N25" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O25" s="19" t="s">
         <v>52</v>
@@ -2900,7 +2967,9 @@
       <c r="T25" s="19">
         <v>6221155643</v>
       </c>
-      <c r="U25" s="2"/>
+      <c r="U25" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V25" s="34" t="s">
         <v>52</v>
       </c>
@@ -2918,32 +2987,32 @@
       <c r="C26" s="2">
         <v>1</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>66</v>
+      <c r="D26" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F26" s="42">
         <v>24</v>
       </c>
       <c r="G26" s="43"/>
-      <c r="H26" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I26" s="34"/>
+      <c r="H26" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="94"/>
       <c r="J26" s="2">
         <v>4999</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>52</v>
+      <c r="K26" s="2">
+        <v>1649</v>
       </c>
       <c r="L26" s="34">
         <v>24</v>
       </c>
       <c r="M26" s="34"/>
       <c r="N26" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O26" s="19" t="s">
         <v>52</v>
@@ -2961,7 +3030,9 @@
       <c r="T26" s="19">
         <v>6221155649</v>
       </c>
-      <c r="U26" s="2"/>
+      <c r="U26" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V26" s="34" t="s">
         <v>52</v>
       </c>
@@ -2979,32 +3050,32 @@
       <c r="C27" s="2">
         <v>1</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>66</v>
+      <c r="D27" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F27" s="42">
         <v>24</v>
       </c>
       <c r="G27" s="43"/>
-      <c r="H27" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" s="34"/>
+      <c r="H27" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="94"/>
       <c r="J27" s="2">
         <v>4999</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>52</v>
+      <c r="K27" s="2">
+        <v>1649</v>
       </c>
       <c r="L27" s="34">
         <v>24</v>
       </c>
       <c r="M27" s="34"/>
       <c r="N27" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O27" s="19" t="s">
         <v>52</v>
@@ -3022,7 +3093,9 @@
       <c r="T27" s="19">
         <v>6221155652</v>
       </c>
-      <c r="U27" s="2"/>
+      <c r="U27" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V27" s="34" t="s">
         <v>52</v>
       </c>
@@ -3040,32 +3113,32 @@
       <c r="C28" s="2">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>66</v>
+      <c r="D28" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F28" s="42">
         <v>24</v>
       </c>
       <c r="G28" s="43"/>
-      <c r="H28" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I28" s="34"/>
+      <c r="H28" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="94"/>
       <c r="J28" s="2">
         <v>4999</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>52</v>
+      <c r="K28" s="2">
+        <v>1649</v>
       </c>
       <c r="L28" s="34">
         <v>24</v>
       </c>
       <c r="M28" s="34"/>
       <c r="N28" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O28" s="19" t="s">
         <v>52</v>
@@ -3083,7 +3156,9 @@
       <c r="T28" s="19">
         <v>6221854807</v>
       </c>
-      <c r="U28" s="2"/>
+      <c r="U28" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V28" s="34" t="s">
         <v>52</v>
       </c>
@@ -3101,32 +3176,32 @@
       <c r="C29" s="2">
         <v>1</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>66</v>
+      <c r="D29" s="90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="90" t="s">
+        <v>68</v>
       </c>
       <c r="F29" s="42">
         <v>24</v>
       </c>
       <c r="G29" s="43"/>
-      <c r="H29" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="I29" s="34"/>
+      <c r="H29" s="93" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="94"/>
       <c r="J29" s="2">
         <v>4999</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>52</v>
+      <c r="K29" s="2">
+        <v>1649</v>
       </c>
       <c r="L29" s="34">
         <v>24</v>
       </c>
       <c r="M29" s="34"/>
       <c r="N29" s="2">
-        <v>208.3</v>
+        <v>139.59</v>
       </c>
       <c r="O29" s="19" t="s">
         <v>52</v>
@@ -3144,7 +3219,9 @@
       <c r="T29" s="19">
         <v>6221156875</v>
       </c>
-      <c r="U29" s="2"/>
+      <c r="U29" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="V29" s="34" t="s">
         <v>52</v>
       </c>
@@ -3245,28 +3322,28 @@
     </row>
     <row r="33" spans="2:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B33" s="7"/>
-      <c r="C33" s="67" t="s">
+      <c r="C33" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="68"/>
-      <c r="E33" s="69" t="s">
+      <c r="D33" s="62"/>
+      <c r="E33" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="69"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="69"/>
-      <c r="S33" s="69"/>
-      <c r="T33" s="70"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="63"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="63"/>
+      <c r="S33" s="63"/>
+      <c r="T33" s="64"/>
       <c r="U33" s="17"/>
       <c r="V33" s="33" t="s">
         <v>48</v>
@@ -3313,26 +3390,26 @@
     </row>
     <row r="35" spans="2:26" ht="18.5" x14ac:dyDescent="0.35">
       <c r="B35" s="7"/>
-      <c r="C35" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="48"/>
+      <c r="C35" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="84"/>
+      <c r="O35" s="84"/>
+      <c r="P35" s="84"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="84"/>
+      <c r="S35" s="84"/>
+      <c r="T35" s="85"/>
       <c r="U35" s="17"/>
       <c r="V35" s="31" t="s">
         <v>33</v>
@@ -3346,26 +3423,26 @@
     </row>
     <row r="36" spans="2:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
-      <c r="C36" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
-      <c r="L36" s="50"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="51"/>
+      <c r="C36" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="87"/>
+      <c r="N36" s="87"/>
+      <c r="O36" s="87"/>
+      <c r="P36" s="87"/>
+      <c r="Q36" s="87"/>
+      <c r="R36" s="87"/>
+      <c r="S36" s="87"/>
+      <c r="T36" s="88"/>
       <c r="U36" s="17"/>
       <c r="V36" s="31" t="s">
         <v>34</v>
@@ -3379,24 +3456,24 @@
     </row>
     <row r="37" spans="2:26" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B37" s="7"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="54"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
+      <c r="P37" s="50"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="50"/>
+      <c r="S37" s="50"/>
+      <c r="T37" s="51"/>
       <c r="U37" s="17"/>
       <c r="V37" s="31" t="s">
         <v>35</v>

--- a/salida/507843056_CORPORATIVO_EN_FARMACIAS_Y_SERVICIOS_ZH_SA_DE_CV/op_borrador.xlsx
+++ b/salida/507843056_CORPORATIVO_EN_FARMACIAS_Y_SERVICIOS_ZH_SA_DE_CV/op_borrador.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="70">
   <si>
     <t>Plan tarifario</t>
   </si>
@@ -221,7 +221,7 @@
     <t>AVENIDA SERDAN 80, INT LOCAL 3, GUAYMAS CENTRO, GUAYMAS, SONORA, 85400</t>
   </si>
   <si>
-    <t>240729MKT0305</t>
+    <t>260922SM0965999</t>
   </si>
   <si>
     <t xml:space="preserve"> PLAN 1299: REDES: Facebook; Intagram; Gmail; Google_maps; Outlook; X; Uber; WhatsApp (Texto);    STREAMING: Spotify; WhatsApp (Video); TikTok; 2 GB</t>
@@ -236,7 +236,7 @@
     <t>ATT Armalo Negocios 1299 CPP CTRL</t>
   </si>
   <si>
-    <t>APPLE IPHONE 18 PRO MAX 256GB 5G, PLATA</t>
+    <t>APPLE IPHONE 18 PRO MAX 256GB 5G, BORGOÑA</t>
   </si>
   <si>
     <t>CPP</t>
@@ -248,7 +248,7 @@
     <t>ATT Armalo Negocios 399 CPP CTRL</t>
   </si>
   <si>
-    <t>GALAXY A14 4G 128GB, BLACK ATT</t>
+    <t>SAMSUNG GALAXY A36 5G, BLACK ATT</t>
   </si>
 </sst>
 </file>
@@ -588,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -830,12 +830,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,16 +1156,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100">
-            <a:ln w="38100">
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100">
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:ln>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
+            </a:rPr>
+            <a:t>7</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1272,16 +1280,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100">
-            <a:ln w="38100">
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100">
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:ln>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
+            </a:rPr>
+            <a:t>13</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1349,16 +1360,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-MX" sz="1100">
-            <a:ln w="38100">
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100">
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:ln>
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-            </a:ln>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
+            </a:rPr>
+            <a:t>19</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2375,17 +2389,17 @@
         <v>31999</v>
       </c>
       <c r="K16" s="26">
-        <v>27199</v>
+        <v>23447.41</v>
       </c>
       <c r="L16" s="52">
         <v>24</v>
       </c>
       <c r="M16" s="53"/>
       <c r="N16" s="26">
-        <v>200.01</v>
-      </c>
-      <c r="O16" s="26" t="s">
-        <v>52</v>
+        <v>356.32</v>
+      </c>
+      <c r="O16" s="93">
+        <v>0.2</v>
       </c>
       <c r="P16" s="26" t="s">
         <v>53</v>
@@ -2395,7 +2409,7 @@
       </c>
       <c r="R16" s="45"/>
       <c r="S16" s="26">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T16" s="26">
         <v>6221201372</v>
@@ -2411,7 +2425,7 @@
         <v>52</v>
       </c>
       <c r="Y16" s="26">
-        <v>1349</v>
+        <v>1079.2</v>
       </c>
       <c r="Z16" s="9"/>
     </row>
@@ -2430,25 +2444,25 @@
         <v>24</v>
       </c>
       <c r="G17" s="43"/>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="94"/>
+      <c r="I17" s="95"/>
       <c r="J17" s="2">
         <v>31999</v>
       </c>
       <c r="K17" s="2">
-        <v>27199</v>
+        <v>23447.41</v>
       </c>
       <c r="L17" s="34">
         <v>24</v>
       </c>
       <c r="M17" s="34"/>
       <c r="N17" s="2">
-        <v>200.01</v>
-      </c>
-      <c r="O17" s="19" t="s">
-        <v>52</v>
+        <v>356.32</v>
+      </c>
+      <c r="O17" s="96">
+        <v>0.2</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>53</v>
@@ -2458,7 +2472,7 @@
       </c>
       <c r="R17" s="34"/>
       <c r="S17" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T17" s="19">
         <v>6221090987</v>
@@ -2474,7 +2488,7 @@
         <v>52</v>
       </c>
       <c r="Y17" s="2">
-        <v>1349</v>
+        <v>1079.2</v>
       </c>
       <c r="Z17" s="9"/>
     </row>
@@ -2493,25 +2507,25 @@
         <v>24</v>
       </c>
       <c r="G18" s="43"/>
-      <c r="H18" s="93" t="s">
+      <c r="H18" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="94"/>
+      <c r="I18" s="95"/>
       <c r="J18" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K18" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L18" s="34">
         <v>24</v>
       </c>
       <c r="M18" s="34"/>
       <c r="N18" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O18" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O18" s="96">
+        <v>0.2</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>53</v>
@@ -2521,7 +2535,7 @@
       </c>
       <c r="R18" s="34"/>
       <c r="S18" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T18" s="19">
         <v>6221155647</v>
@@ -2537,7 +2551,7 @@
         <v>52</v>
       </c>
       <c r="Y18" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z18" s="9"/>
     </row>
@@ -2556,25 +2570,25 @@
         <v>24</v>
       </c>
       <c r="G19" s="43"/>
-      <c r="H19" s="93" t="s">
+      <c r="H19" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="94"/>
+      <c r="I19" s="95"/>
       <c r="J19" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K19" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L19" s="34">
         <v>24</v>
       </c>
       <c r="M19" s="34"/>
       <c r="N19" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O19" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O19" s="96">
+        <v>0.2</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>53</v>
@@ -2584,7 +2598,7 @@
       </c>
       <c r="R19" s="34"/>
       <c r="S19" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T19" s="19">
         <v>6221155645</v>
@@ -2600,7 +2614,7 @@
         <v>52</v>
       </c>
       <c r="Y19" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z19" s="9"/>
     </row>
@@ -2619,25 +2633,25 @@
         <v>24</v>
       </c>
       <c r="G20" s="43"/>
-      <c r="H20" s="93" t="s">
+      <c r="H20" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I20" s="94"/>
+      <c r="I20" s="95"/>
       <c r="J20" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K20" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L20" s="34">
         <v>24</v>
       </c>
       <c r="M20" s="34"/>
       <c r="N20" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O20" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O20" s="96">
+        <v>0.2</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>53</v>
@@ -2647,7 +2661,7 @@
       </c>
       <c r="R20" s="34"/>
       <c r="S20" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T20" s="19">
         <v>6221155658</v>
@@ -2663,7 +2677,7 @@
         <v>52</v>
       </c>
       <c r="Y20" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z20" s="9"/>
     </row>
@@ -2682,25 +2696,25 @@
         <v>24</v>
       </c>
       <c r="G21" s="43"/>
-      <c r="H21" s="93" t="s">
+      <c r="H21" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I21" s="94"/>
+      <c r="I21" s="95"/>
       <c r="J21" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K21" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L21" s="34">
         <v>24</v>
       </c>
       <c r="M21" s="34"/>
       <c r="N21" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O21" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O21" s="96">
+        <v>0.2</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>53</v>
@@ -2710,7 +2724,7 @@
       </c>
       <c r="R21" s="34"/>
       <c r="S21" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T21" s="19">
         <v>6221854808</v>
@@ -2726,7 +2740,7 @@
         <v>52</v>
       </c>
       <c r="Y21" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z21" s="9"/>
     </row>
@@ -2745,25 +2759,25 @@
         <v>24</v>
       </c>
       <c r="G22" s="43"/>
-      <c r="H22" s="93" t="s">
+      <c r="H22" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="94"/>
+      <c r="I22" s="95"/>
       <c r="J22" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K22" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L22" s="34">
         <v>24</v>
       </c>
       <c r="M22" s="34"/>
       <c r="N22" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O22" s="96">
+        <v>0.2</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>53</v>
@@ -2773,7 +2787,7 @@
       </c>
       <c r="R22" s="34"/>
       <c r="S22" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T22" s="19">
         <v>6221155654</v>
@@ -2789,7 +2803,7 @@
         <v>52</v>
       </c>
       <c r="Y22" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z22" s="9"/>
     </row>
@@ -2808,25 +2822,25 @@
         <v>24</v>
       </c>
       <c r="G23" s="43"/>
-      <c r="H23" s="93" t="s">
+      <c r="H23" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I23" s="94"/>
+      <c r="I23" s="95"/>
       <c r="J23" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K23" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L23" s="34">
         <v>24</v>
       </c>
       <c r="M23" s="34"/>
       <c r="N23" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O23" s="97">
+        <v>0.2</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>53</v>
@@ -2836,7 +2850,7 @@
       </c>
       <c r="R23" s="34"/>
       <c r="S23" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T23" s="2">
         <v>6221854809</v>
@@ -2852,7 +2866,7 @@
         <v>52</v>
       </c>
       <c r="Y23" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z23" s="9"/>
     </row>
@@ -2871,25 +2885,25 @@
         <v>24</v>
       </c>
       <c r="G24" s="43"/>
-      <c r="H24" s="93" t="s">
+      <c r="H24" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="94"/>
+      <c r="I24" s="95"/>
       <c r="J24" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K24" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L24" s="34">
         <v>24</v>
       </c>
       <c r="M24" s="34"/>
       <c r="N24" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O24" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O24" s="96">
+        <v>0.2</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>53</v>
@@ -2899,7 +2913,7 @@
       </c>
       <c r="R24" s="34"/>
       <c r="S24" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T24" s="19">
         <v>6221155655</v>
@@ -2915,7 +2929,7 @@
         <v>52</v>
       </c>
       <c r="Y24" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z24" s="9"/>
     </row>
@@ -2934,25 +2948,25 @@
         <v>24</v>
       </c>
       <c r="G25" s="43"/>
-      <c r="H25" s="93" t="s">
+      <c r="H25" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="94"/>
+      <c r="I25" s="95"/>
       <c r="J25" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K25" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L25" s="34">
         <v>24</v>
       </c>
       <c r="M25" s="34"/>
       <c r="N25" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O25" s="96">
+        <v>0.2</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>53</v>
@@ -2962,7 +2976,7 @@
       </c>
       <c r="R25" s="34"/>
       <c r="S25" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T25" s="19">
         <v>6221155643</v>
@@ -2978,7 +2992,7 @@
         <v>52</v>
       </c>
       <c r="Y25" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z25" s="9"/>
     </row>
@@ -2997,25 +3011,25 @@
         <v>24</v>
       </c>
       <c r="G26" s="43"/>
-      <c r="H26" s="93" t="s">
+      <c r="H26" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="94"/>
+      <c r="I26" s="95"/>
       <c r="J26" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K26" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L26" s="34">
         <v>24</v>
       </c>
       <c r="M26" s="34"/>
       <c r="N26" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O26" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O26" s="96">
+        <v>0.2</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>53</v>
@@ -3025,7 +3039,7 @@
       </c>
       <c r="R26" s="34"/>
       <c r="S26" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T26" s="19">
         <v>6221155649</v>
@@ -3041,7 +3055,7 @@
         <v>52</v>
       </c>
       <c r="Y26" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z26" s="9"/>
     </row>
@@ -3060,25 +3074,25 @@
         <v>24</v>
       </c>
       <c r="G27" s="43"/>
-      <c r="H27" s="93" t="s">
+      <c r="H27" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="94"/>
+      <c r="I27" s="95"/>
       <c r="J27" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K27" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L27" s="34">
         <v>24</v>
       </c>
       <c r="M27" s="34"/>
       <c r="N27" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O27" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O27" s="96">
+        <v>0.2</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>53</v>
@@ -3088,7 +3102,7 @@
       </c>
       <c r="R27" s="34"/>
       <c r="S27" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T27" s="19">
         <v>6221155652</v>
@@ -3104,7 +3118,7 @@
         <v>52</v>
       </c>
       <c r="Y27" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z27" s="9"/>
     </row>
@@ -3123,25 +3137,25 @@
         <v>24</v>
       </c>
       <c r="G28" s="43"/>
-      <c r="H28" s="93" t="s">
+      <c r="H28" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="94"/>
+      <c r="I28" s="95"/>
       <c r="J28" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K28" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L28" s="34">
         <v>24</v>
       </c>
       <c r="M28" s="34"/>
       <c r="N28" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O28" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O28" s="96">
+        <v>0.2</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>53</v>
@@ -3151,7 +3165,7 @@
       </c>
       <c r="R28" s="34"/>
       <c r="S28" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T28" s="19">
         <v>6221854807</v>
@@ -3167,7 +3181,7 @@
         <v>52</v>
       </c>
       <c r="Y28" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z28" s="9"/>
     </row>
@@ -3186,25 +3200,25 @@
         <v>24</v>
       </c>
       <c r="G29" s="43"/>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="I29" s="94"/>
+      <c r="I29" s="95"/>
       <c r="J29" s="2">
-        <v>4999</v>
+        <v>7499</v>
       </c>
       <c r="K29" s="2">
-        <v>1649</v>
+        <v>1300.75</v>
       </c>
       <c r="L29" s="34">
         <v>24</v>
       </c>
       <c r="M29" s="34"/>
       <c r="N29" s="2">
-        <v>139.59</v>
-      </c>
-      <c r="O29" s="19" t="s">
-        <v>52</v>
+        <v>258.27</v>
+      </c>
+      <c r="O29" s="96">
+        <v>0.2</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>53</v>
@@ -3214,7 +3228,7 @@
       </c>
       <c r="R29" s="34"/>
       <c r="S29" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T29" s="19">
         <v>6221156875</v>
@@ -3230,7 +3244,7 @@
         <v>52</v>
       </c>
       <c r="Y29" s="2">
-        <v>449</v>
+        <v>359.2</v>
       </c>
       <c r="Z29" s="9"/>
     </row>
@@ -3289,7 +3303,7 @@
       <c r="X31" s="37"/>
       <c r="Y31" s="29">
         <f>SUM(Y16:Y30)</f>
-        <v>8086</v>
+        <v>6468.7999999999984</v>
       </c>
       <c r="Z31" s="9"/>
     </row>
